--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_REINA PROTEÍNAS CLAVIJO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_REINA PROTEÍNAS CLAVIJO.xlsx
@@ -565,67 +565,67 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.532</v>
+        <v>5.4407</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2226</v>
+        <v>3.3219</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3093</v>
+        <v>2.1188</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2939</v>
+        <v>1.2358</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8949</v>
+        <v>1.8599</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6009</v>
+        <v>-0.6242</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1822</v>
+        <v>1.2359</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0596</v>
+        <v>1.0859</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1225999999999999</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1116999999999999</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8353</v>
+        <v>0.7741</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7235</v>
+        <v>-0.7741999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0727</v>
+        <v>3.0368</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0727</v>
+        <v>3.0368</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7414999999999998</v>
+        <v>0.7423</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2081</v>
+        <v>1.2401</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4666</v>
+        <v>-0.4977</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4238</v>
+        <v>0.4259</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4085</v>
+        <v>-0.4201</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6774</v>
+        <v>0.6406999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4699</v>
+        <v>2.6165</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7925</v>
+        <v>-1.9758</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6309</v>
+        <v>4.626300000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8204</v>
+        <v>5.8496</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.1895</v>
+        <v>-1.2234</v>
       </c>
       <c r="J3" t="n">
-        <v>5.122199999999999</v>
+        <v>5.1966</v>
       </c>
       <c r="K3" t="n">
-        <v>4.845499999999999</v>
+        <v>4.9183</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2766</v>
+        <v>0.2783</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4912</v>
+        <v>-0.5704</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9749000000000001</v>
+        <v>0.9312</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4661</v>
+        <v>-1.5017</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8193</v>
+        <v>-0.8099000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9224</v>
+        <v>0.9083000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3958</v>
+        <v>0.3585</v>
       </c>
       <c r="V3" t="n">
-        <v>-4.0565</v>
+        <v>-4.084</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1061</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.9504</v>
+        <v>-3.9907</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2248999999999999</v>
+        <v>0.2804</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1547</v>
+        <v>-0.9446000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3796</v>
+        <v>1.225</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6297999999999999</v>
+        <v>-0.6272999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8303000000000003</v>
+        <v>0.8113999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4601</v>
+        <v>-1.4387</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2094</v>
+        <v>0.3107</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1102</v>
+        <v>1.1636</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.8529</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2798</v>
+        <v>-0.3521</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5593</v>
+        <v>-0.5859000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0484</v>
+        <v>-2.0246</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.3261</v>
+        <v>-5.2637</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2775</v>
+        <v>3.2393</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5421</v>
+        <v>0.5518000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.707</v>
+        <v>1.7213</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1649</v>
+        <v>-1.1695</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2551</v>
+        <v>2.2871</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1062</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2436</v>
+        <v>-1.2705</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1248</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1188</v>
+        <v>-0.2849999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2066</v>
+        <v>-2.2032</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5492</v>
+        <v>0.5533</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.7558</v>
+        <v>-2.7564</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5628</v>
+        <v>-1.4815</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3549</v>
+        <v>0.4122</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9177</v>
+        <v>-1.8937</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6437999999999999</v>
+        <v>-0.7216</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1943</v>
+        <v>0.1411000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8380000000000001</v>
+        <v>-0.8627</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4097000000000001</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.277600000000001</v>
+        <v>-3.2392</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8678</v>
+        <v>2.8344</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7954</v>
+        <v>2.7787</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2315</v>
+        <v>3.2335</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4360999999999999</v>
+        <v>-0.4548</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4841000000000001</v>
+        <v>0.5018999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9068</v>
+        <v>-1.943</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3251</v>
+        <v>-1.3653</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4271</v>
+        <v>-1.2336</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1019000000000001</v>
+        <v>-0.1316999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.627</v>
+        <v>-1.667</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8371</v>
+        <v>-1.8571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2101</v>
+        <v>0.1899999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.494</v>
+        <v>-0.4072</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1947</v>
+        <v>-1.13</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7008000000000001</v>
+        <v>0.7229</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.133</v>
+        <v>-1.2598</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6424000000000001</v>
+        <v>-0.727</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4906</v>
+        <v>-0.5327000000000002</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.4582</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.350300000000001</v>
+        <v>-6.276</v>
       </c>
       <c r="R6" t="n">
-        <v>3.8921</v>
+        <v>3.8466</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1567</v>
+        <v>3.1254</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4043</v>
+        <v>3.4133</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2476</v>
+        <v>-0.2879</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3967000000000003</v>
+        <v>-0.3943999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>2.013</v>
+        <v>2.0362</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4096</v>
+        <v>-2.4306</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9237</v>
+        <v>-2.9341</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3047</v>
+        <v>-3.1921</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3807999999999999</v>
+        <v>0.2580000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0791</v>
+        <v>-1.0895</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4853</v>
+        <v>1.4638</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.5644</v>
+        <v>-2.5533</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1469</v>
+        <v>-0.0861</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6498</v>
+        <v>0.671</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7967</v>
+        <v>-0.7571</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9322</v>
+        <v>-1.0033</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8355</v>
+        <v>0.7928999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7677</v>
+        <v>-1.7962</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4097</v>
+        <v>-0.4048999999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6387</v>
+        <v>1.6197</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7265999999999999</v>
+        <v>-0.7256</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7609</v>
+        <v>-0.7373000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03439999999999999</v>
+        <v>0.01170000000000002</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7082999999999999</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3601</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9099</v>
+        <v>-3.887</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.3146</v>
+        <v>-5.0565</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4047</v>
+        <v>1.1695</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.290500000000001</v>
+        <v>-4.23</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.44</v>
+        <v>-4.4285</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1495000000000006</v>
+        <v>0.1985000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.8023</v>
+        <v>-4.6299</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.303</v>
+        <v>-5.2227</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5007999999999999</v>
+        <v>0.5927000000000002</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5117</v>
+        <v>0.3999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.863</v>
+        <v>0.7942</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3512</v>
+        <v>-0.3944</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8679</v>
+        <v>2.8343</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R8" t="n">
-        <v>4.097</v>
+        <v>4.048999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1849</v>
+        <v>-2.1644</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.6444</v>
+        <v>-1.5924</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5404</v>
+        <v>-0.5720999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3023</v>
+        <v>-0.3269000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3612</v>
+        <v>2.3804</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.6635</v>
+        <v>-2.7073</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8687</v>
+        <v>-4.8612</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3203</v>
+        <v>-3.2842</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5485</v>
+        <v>-1.577</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.7939</v>
+        <v>-3.8017</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9512</v>
+        <v>-1.9567</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.8427</v>
+        <v>-1.845</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0508</v>
+        <v>-2.0365</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3935</v>
+        <v>-1.3842</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7432</v>
+        <v>-1.7651</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5577</v>
+        <v>-0.5725</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1855</v>
+        <v>-1.1926</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2554</v>
+        <v>-0.2497</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2453</v>
+        <v>-0.2354</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0102</v>
+        <v>-0.0143</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,67 +1189,67 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2182</v>
+        <v>-5.1523</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.588</v>
+        <v>-4.2943</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6303000000000001</v>
+        <v>-0.8580999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2805</v>
+        <v>-0.2774999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6354</v>
+        <v>1.584</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9157</v>
+        <v>-1.8616</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4758</v>
+        <v>1.6188</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5533</v>
+        <v>1.5988</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.07740000000000036</v>
+        <v>0.01989999999999981</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7563</v>
+        <v>-1.8964</v>
       </c>
       <c r="N10" t="n">
-        <v>0.08210000000000006</v>
+        <v>-0.01479999999999998</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8383</v>
+        <v>-1.8815</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.3261</v>
+        <v>-5.2637</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4824</v>
+        <v>3.4417</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.2877</v>
+        <v>-3.2535</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.0541</v>
+        <v>-1.9973</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2336</v>
+        <v>-1.2563</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1937</v>
+        <v>0.2007</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3165</v>
+        <v>1.3479</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1228</v>
+        <v>-1.1472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3987</v>
+        <v>-6.3174</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.161100000000001</v>
+        <v>-7.8795</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7624</v>
+        <v>1.562</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3168</v>
+        <v>0.3271</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1921</v>
+        <v>0.1786</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1246</v>
+        <v>0.1485</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4787999999999999</v>
+        <v>-0.3709</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6989</v>
+        <v>-0.6546000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2201</v>
+        <v>0.2837999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7955999999999999</v>
+        <v>0.698</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8911</v>
+        <v>0.8331</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.09549999999999997</v>
+        <v>-0.1352</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.3018</v>
+        <v>-4.2515</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.193899999999999</v>
+        <v>-8.098100000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>3.8921</v>
+        <v>3.8466</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9473</v>
+        <v>-1.93</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.7434</v>
+        <v>-1.6978</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2039</v>
+        <v>-0.2322</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4663</v>
+        <v>-0.4632</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2551</v>
+        <v>2.2871</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7213</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.45359999999999</v>
+        <v>-19.426</v>
       </c>
       <c r="E12" t="n">
-        <v>-22.7028</v>
+        <v>-20.9318</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2486</v>
+        <v>1.5057</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.665800000000002</v>
+        <v>-7.706999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1793</v>
+        <v>4.058300000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.8449</v>
+        <v>-11.7656</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.546</v>
+        <v>-0.6500999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9831999999999984</v>
+        <v>1.458300000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5288</v>
+        <v>-2.1084</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.119899999999999</v>
+        <v>-7.056799999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1963</v>
+        <v>2.6002</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.3157</v>
+        <v>-9.657099999999998</v>
       </c>
       <c r="P12" t="n">
-        <v>-7.1695</v>
+        <v>-7.086</v>
       </c>
       <c r="Q12" t="n">
-        <v>-35.8485</v>
+        <v>-35.429</v>
       </c>
       <c r="R12" t="n">
-        <v>28.6784</v>
+        <v>28.3436</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2437999999999991</v>
+        <v>-0.2167000000000006</v>
       </c>
       <c r="T12" t="n">
-        <v>3.629500000000001</v>
+        <v>3.897900000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.8731</v>
+        <v>-4.1146</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.374099999999999</v>
+        <v>-4.416799999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>11.0631</v>
+        <v>11.2491</v>
       </c>
       <c r="X12" t="n">
-        <v>-15.4368</v>
+        <v>-15.6661</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_REINA PROTEÍNAS CLAVIJO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate_individual/AGG_IND_REINA PROTEÍNAS CLAVIJO.xlsx
@@ -565,13 +565,13 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4407</v>
+        <v>4.8156</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3219</v>
+        <v>2.668</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1188</v>
+        <v>2.1476</v>
       </c>
       <c r="G2" t="n">
         <v>1.2358</v>
@@ -610,13 +610,13 @@
         <v>3.0368</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7423</v>
+        <v>0.1172</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2401</v>
+        <v>0.5861000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4977</v>
+        <v>-0.4689</v>
       </c>
       <c r="V2" t="n">
         <v>0.4259</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6406999999999999</v>
+        <v>0.5297000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6165</v>
+        <v>-1.2716</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9758</v>
+        <v>1.8013</v>
       </c>
       <c r="G3" t="n">
-        <v>4.626300000000001</v>
+        <v>-0.6272999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8496</v>
+        <v>0.8113999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2234</v>
+        <v>-1.4387</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1966</v>
+        <v>0.3107</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9183</v>
+        <v>1.1636</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2783</v>
+        <v>-0.8529</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5704</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9312</v>
+        <v>-0.3521</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5017</v>
+        <v>-0.5859000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8099000000000001</v>
+        <v>-2.0246</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0368</v>
+        <v>-5.2637</v>
       </c>
       <c r="R3" t="n">
-        <v>2.227</v>
+        <v>3.2393</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9083000000000001</v>
+        <v>0.8011</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5499000000000001</v>
+        <v>1.3943</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3585</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-4.084</v>
+        <v>2.3804</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.09329999999999999</v>
+        <v>2.2871</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.9907</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2804</v>
+        <v>0.1249</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9446000000000001</v>
+        <v>2.4176</v>
       </c>
       <c r="F4" t="n">
-        <v>1.225</v>
+        <v>-2.2927</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6272999999999999</v>
+        <v>4.626300000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8113999999999999</v>
+        <v>5.8496</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4387</v>
+        <v>-1.2234</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3107</v>
+        <v>5.1966</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1636</v>
+        <v>4.9183</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8529</v>
+        <v>0.2783</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-0.5704</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3521</v>
+        <v>0.9312</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5859000000000001</v>
+        <v>-1.5017</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0246</v>
+        <v>-0.8099000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.2637</v>
+        <v>-3.0368</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2393</v>
+        <v>2.227</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5518000000000001</v>
+        <v>0.3925</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7213</v>
+        <v>0.351</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1695</v>
+        <v>0.0415</v>
       </c>
       <c r="V4" t="n">
-        <v>2.3804</v>
+        <v>-4.084</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2871</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0.09320000000000001</v>
+        <v>-3.9907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2705</v>
+        <v>-2.0268</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-2.1695</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2849999999999999</v>
+        <v>0.1428</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2032</v>
+        <v>-1.0895</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5533</v>
+        <v>1.4638</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.7564</v>
+        <v>-2.5533</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4815</v>
+        <v>-0.0861</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4122</v>
+        <v>0.671</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.8937</v>
+        <v>-0.7571</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7216</v>
+        <v>-1.0033</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1411000000000001</v>
+        <v>0.7928999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8627</v>
+        <v>-1.7962</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4049</v>
+        <v>-0.4048999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.2392</v>
+        <v>-2.0245</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8344</v>
+        <v>1.6197</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7787</v>
+        <v>0.1817</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2335</v>
+        <v>0.2852</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4548</v>
+        <v>-0.1035</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4411</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5018999999999999</v>
+        <v>-0.3442</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.943</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3653</v>
+        <v>-2.1487</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2336</v>
+        <v>-3.347</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1316999999999999</v>
+        <v>1.1983</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.667</v>
+        <v>-4.23</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8571</v>
+        <v>-4.4285</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1899999999999999</v>
+        <v>0.1985000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4072</v>
+        <v>-4.6299</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.13</v>
+        <v>-5.2227</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7229</v>
+        <v>0.5927000000000002</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2598</v>
+        <v>0.3999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.727</v>
+        <v>0.7942</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5327000000000002</v>
+        <v>-0.3944</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.4294</v>
+        <v>2.8343</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.276</v>
+        <v>-1.2147</v>
       </c>
       <c r="R6" t="n">
-        <v>3.8466</v>
+        <v>4.048999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>3.1254</v>
+        <v>-0.4261</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4133</v>
+        <v>0.1172</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2879</v>
+        <v>-0.5432</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3943999999999999</v>
+        <v>-0.3269000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>2.0362</v>
+        <v>2.3804</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4306</v>
+        <v>-2.7073</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.9341</v>
+        <v>-2.5958</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.1921</v>
+        <v>-2.3107</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2580000000000001</v>
+        <v>-0.2851</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0895</v>
+        <v>-2.2032</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4638</v>
+        <v>0.5533</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.5533</v>
+        <v>-2.7564</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0861</v>
+        <v>-1.4815</v>
       </c>
       <c r="K7" t="n">
-        <v>0.671</v>
+        <v>0.4122</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7571</v>
+        <v>-1.8937</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0033</v>
+        <v>-0.7216</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7928999999999999</v>
+        <v>0.1411000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7962</v>
+        <v>-0.8627</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4048999999999999</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0245</v>
+        <v>-3.2392</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6197</v>
+        <v>2.8344</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7256</v>
+        <v>1.4534</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7373000000000001</v>
+        <v>1.9082</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01170000000000002</v>
+        <v>-0.4548</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-1.4411</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3442</v>
+        <v>0.5018999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.37</v>
+        <v>-1.943</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.887</v>
+        <v>-2.905400000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.0565</v>
+        <v>-2.2491</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1695</v>
+        <v>-0.6564999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.23</v>
+        <v>-0.2774999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.4285</v>
+        <v>1.584</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1985000000000001</v>
+        <v>-1.8616</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.6299</v>
+        <v>1.6188</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.2227</v>
+        <v>1.5988</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5927000000000002</v>
+        <v>0.01989999999999981</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3999</v>
+        <v>-1.8964</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7942</v>
+        <v>-0.01479999999999998</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3944</v>
+        <v>-1.8815</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8343</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2147</v>
+        <v>-5.2637</v>
       </c>
       <c r="R8" t="n">
-        <v>4.048999999999999</v>
+        <v>3.4417</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.1644</v>
+        <v>-1.0066</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5924</v>
+        <v>0.04790000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5720999999999999</v>
+        <v>-1.0545</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3269000000000001</v>
+        <v>0.2007</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3804</v>
+        <v>1.3479</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7073</v>
+        <v>-1.1472</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8612</v>
+        <v>-3.8034</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2842</v>
+        <v>-3.1818</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.577</v>
+        <v>-0.6215999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.8017</v>
+        <v>-1.667</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9567</v>
+        <v>-1.8571</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.845</v>
+        <v>0.1899999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0365</v>
+        <v>-0.4072</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3842</v>
+        <v>-1.13</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6523</v>
+        <v>0.7229</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7651</v>
+        <v>-1.2598</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5725</v>
+        <v>-0.727</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1926</v>
+        <v>-0.5327000000000002</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.8098</v>
+        <v>-2.4294</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0123</v>
+        <v>-6.276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2025</v>
+        <v>3.8466</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2497</v>
+        <v>0.6874</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2354</v>
+        <v>1.4651</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0143</v>
+        <v>-0.7777000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3943999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.0362</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.4306</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1523</v>
+        <v>-4.3312</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2943</v>
+        <v>-6.0661</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8580999999999999</v>
+        <v>1.7349</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2774999999999999</v>
+        <v>0.3271</v>
       </c>
       <c r="H10" t="n">
-        <v>1.584</v>
+        <v>0.1786</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8616</v>
+        <v>0.1485</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6188</v>
+        <v>-0.3709</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5988</v>
+        <v>-0.6546000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01989999999999981</v>
+        <v>0.2837999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8964</v>
+        <v>0.698</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.01479999999999998</v>
+        <v>0.8331</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8815</v>
+        <v>-0.1352</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8221</v>
+        <v>-4.2515</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.2637</v>
+        <v>-8.098100000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4417</v>
+        <v>3.8466</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.2535</v>
+        <v>0.05630000000000002</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9973</v>
+        <v>0.1155</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2563</v>
+        <v>-0.05929999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2007</v>
+        <v>-0.4632</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3479</v>
+        <v>2.2871</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.1472</v>
+        <v>-2.7504</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3174</v>
+        <v>-4.8438</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.8795</v>
+        <v>-3.1804</v>
       </c>
       <c r="F11" t="n">
-        <v>1.562</v>
+        <v>-1.6634</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3271</v>
+        <v>-3.8017</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1786</v>
+        <v>-1.9567</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1485</v>
+        <v>-1.845</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3709</v>
+        <v>-2.0365</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6546000000000001</v>
+        <v>-1.3842</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2837999999999999</v>
+        <v>-0.6523</v>
       </c>
       <c r="M11" t="n">
-        <v>0.698</v>
+        <v>-1.7651</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8331</v>
+        <v>-0.5725</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1352</v>
+        <v>-1.1926</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.2515</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q11" t="n">
-        <v>-8.098100000000001</v>
+        <v>-1.0123</v>
       </c>
       <c r="R11" t="n">
-        <v>3.8466</v>
+        <v>0.2025</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.93</v>
+        <v>-0.2324</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6978</v>
+        <v>-0.1316</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2322</v>
+        <v>-0.1007</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4632</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2871</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,25 +1345,25 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.426</v>
+        <v>-17.1849</v>
       </c>
       <c r="E12" t="n">
-        <v>-20.9318</v>
+        <v>-18.6906</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5057</v>
+        <v>1.5056</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.706999999999999</v>
+        <v>-7.707</v>
       </c>
       <c r="H12" t="n">
-        <v>4.058300000000002</v>
+        <v>4.058300000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-11.7656</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6500999999999999</v>
+        <v>-0.6501000000000003</v>
       </c>
       <c r="K12" t="n">
         <v>1.458300000000001</v>
@@ -1372,31 +1372,31 @@
         <v>-2.1084</v>
       </c>
       <c r="M12" t="n">
-        <v>-7.056799999999999</v>
+        <v>-7.056800000000001</v>
       </c>
       <c r="N12" t="n">
         <v>2.6002</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.657099999999998</v>
+        <v>-9.6571</v>
       </c>
       <c r="P12" t="n">
         <v>-7.086</v>
       </c>
       <c r="Q12" t="n">
-        <v>-35.429</v>
+        <v>-35.42900000000001</v>
       </c>
       <c r="R12" t="n">
         <v>28.3436</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2167000000000006</v>
+        <v>2.024500000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>3.897900000000001</v>
+        <v>6.1389</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.1146</v>
+        <v>-4.1143</v>
       </c>
       <c r="V12" t="n">
         <v>-4.416799999999999</v>
